--- a/misc/customizing-label.xlsx
+++ b/misc/customizing-label.xlsx
@@ -9,7 +9,7 @@
     <sheet name="rowsForView" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">rowsForView!$A$1:$F$25</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -99,7 +99,8 @@
     <col min="2" max="2" width="31.0234375" customWidth="true"/>
     <col min="3" max="3" width="255.0" customWidth="true"/>
     <col min="4" max="4" width="27.34375" customWidth="true"/>
-    <col min="5" max="5" width="11.71875" customWidth="true"/>
+    <col min="5" max="5" width="27.34375" customWidth="true"/>
+    <col min="6" max="6" width="11.71875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -120,10 +121,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Translation-German</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -147,10 +153,15 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:sekretariat@lit.gess.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;sekretariat@lit.gess.ethz.ch&lt;/a&gt; möglich.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -172,10 +183,15 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach Voranmeldung bei &lt;a href="mailto:archiv@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;archiv@library.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -197,10 +213,15 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+          <t>&lt;a href="https://registration.slsp.ch/libraries?search={{code}}" target="_blank"&gt;{{libraryName}}&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>45966.0</v>
       </c>
     </row>
@@ -222,10 +243,15 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/lesesaal.html" target="_blank" &gt;ETH-Bibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>45966.0</v>
       </c>
     </row>
@@ -247,10 +273,15 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/baubibliothek.html" target="_blank" &gt;Baubibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>45966.0</v>
       </c>
     </row>
@@ -272,10 +303,15 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
+          <t>&lt;a href="https://lit.ethz.ch/die-gruppe/wie-sie-uns-finden.html" target="_blank"&gt;Professur für Literatur- und Kulturwissenschaft&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>45966.0</v>
       </c>
     </row>
@@ -297,10 +333,15 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
+          <t>Lizenzierte E-Ressourcen der ETH-Bibliothek sind über das ETH-Netzwerk oder</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -322,10 +363,15 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
+          <t xml:space="preserve"> zugänglich.</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -347,10 +393,15 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
+          <t>https://unlimited.ethz.ch/help/network/vpn</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -372,10 +423,15 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
+          <t>VPN</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -397,10 +453,15 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
+          <t>&lt;a href="https://ethz.ch/staffnet/de/anstellung-und-arbeit/arbeitsumfeld/diversity.html" target="_blank"&gt;ETH Diversity&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -422,10 +483,15 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
+          <t>Die Bibliothek Professur für Literatur- und Kulturwissenschaft befindet sich &lt;strong&gt;nicht&lt;/strong&gt; in der GESS-Bibliothek.&lt;br&gt; &lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:diversity@ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;diversity@ethz.ch&lt;/a&gt; möglich.</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>45967.0</v>
       </c>
     </row>
@@ -447,10 +513,15 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
+          <t>Möchten Sie einen Scan eines Artikels oder Kapitels aus diesem Dokument bestellen? &lt;a href="mailto:infodesk@chem.ethz.ch?subject=Scan-Anfrage: MMS ID {{id}}"&gt;Schreiben Sie uns!&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -472,10 +543,15 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
+          <t>&lt;a href="https://infozentrum.ethz.ch/" target="_blank" &gt;ETH Infozentrum Chemie Biologie Pharmazie&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -497,10 +573,15 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/archivieren-und-digitalisieren/archivieren/hochschularchiv-der-eth-zuerich.html" target="_blank" &gt;Hochschularchiv der ETH Zürich&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -522,10 +603,15 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/max-frisch-archiv.html" target="_blank" &gt;ETH Max Frisch-Archiv&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -547,10 +633,15 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/thomas-mann-archiv.html" target="_blank" &gt;ETH Thomas-Mann-Archiv&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -572,10 +663,15 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
+          <t xml:space="preserve">Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:mfa@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;mfa@library.ethz.ch&lt;/a&gt; </t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -597,10 +693,15 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
+          <t xml:space="preserve">Benutzung nur vor Ort. Auskunft erhalten Sie per E-Mail an: &lt;a href="mailto:tma@library.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;tma@library.ethz.ch&lt;/a&gt; </t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -622,10 +723,15 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
+          <t>&lt;a href="https://library.ethz.ch/standorte-und-medien/standorte-und-oeffnungszeiten/graphische-sammlung.html" target="_blank" &gt;ETH Graphische Sammlung&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -647,10 +753,15 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
+          <t xml:space="preserve">Benutzung vor Ort nur nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gs.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gs.ethz.ch&lt;/a&gt; </t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -672,10 +783,15 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
+          <t>&lt;a href="https://archiv.gta.arch.ethz.ch/de/bibliothek" target="_blank" &gt;ETH gta Bibliothek&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -697,10 +813,15 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
+          <t>&lt;strong&gt;Benutzung nur vor Ort&lt;/strong&gt; nach bestätigter Voranmeldung bei &lt;a href="mailto:bibliothek@gta.arch.ethz.ch?subject=Voranmeldung für Benutzung vor Ort von MMS ID {{id}}"&gt;bibliothek@gta.arch.ethz.ch&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
@@ -722,15 +843,20 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>bernd.uttenweiler@library.ethz.ch</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
+          <t>&lt;a href="https://afz.ethz.ch/recherche-archivbesuch/recherche/bibliothek.html" target="_blank" &gt;Archiv für Zeitgeschichte&lt;a&gt;</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>bernd.uttenweiler@library.ethz.ch</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>45968.0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>
